--- a/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
+++ b/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonçalo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonçalo\IdeaProjects\sem3-pi-2024_25_G145_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECA5CB3-9121-4027-8904-34710C63D5B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9639C6C-4576-41CF-B124-34C43AC7A411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="3510" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -3115,10 +3115,10 @@
         <v>154</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="10" t="s">
@@ -3145,7 +3145,7 @@
         <v>155</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C25" s="24">
         <v>4</v>
@@ -3175,7 +3175,7 @@
         <v>156</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" s="24">
         <v>4</v>
@@ -4760,6 +4760,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010097D51C9FBC39324EBAB59B01C4346E09" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7b26372eee874d7f4c5a56df6f7c7ecb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xmlns:ns4="fe0433fa-6222-408a-8cda-04e271f5cb7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5c97cb8d9fdd9979f1f4b37be720903" ns3:_="" ns4:_="">
     <xsd:import namespace="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
@@ -4948,14 +4956,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
   <ds:schemaRefs>
@@ -4965,6 +4965,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0018C3F5-B04E-47AD-B664-46B81F9081B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4981,14 +4991,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
+++ b/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonçalo\IdeaProjects\sem3-pi-2024_25_G145_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9639C6C-4576-41CF-B124-34C43AC7A411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F77DCC4-1F32-416E-B43A-84552096950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="3510" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="167">
   <si>
     <t>LAPR3 Project Team and Self-assessment v4.0</t>
   </si>
@@ -595,9 +595,6 @@
   </si>
   <si>
     <t>USLP05</t>
-  </si>
-  <si>
-    <t>USLP06</t>
   </si>
   <si>
     <t>USAC01</t>
@@ -2475,7 +2472,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
@@ -3110,30 +3107,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>154</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24" s="24">
         <v>4</v>
       </c>
-      <c r="D24" s="44"/>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="45"/>
+      <c r="E24" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="19" t="s">
         <v>41</v>
       </c>
       <c r="J24" s="28" t="s">
@@ -3205,7 +3202,7 @@
         <v>157</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C27" s="24">
         <v>4</v>
@@ -3295,7 +3292,7 @@
         <v>160</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C30" s="24">
         <v>4</v>
@@ -3328,7 +3325,7 @@
         <v>9</v>
       </c>
       <c r="C31" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="45"/>
       <c r="E31" s="18" t="s">
@@ -3355,7 +3352,7 @@
         <v>162</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" s="24">
         <v>5</v>
@@ -3385,7 +3382,7 @@
         <v>163</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C33" s="24">
         <v>5</v>
@@ -3415,10 +3412,10 @@
         <v>164</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34" s="45"/>
       <c r="E34" s="18" t="s">
@@ -3445,10 +3442,10 @@
         <v>165</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C35" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="45"/>
       <c r="E35" s="18" t="s">
@@ -3475,7 +3472,7 @@
         <v>166</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C36" s="24">
         <v>5</v>
@@ -3497,36 +3494,6 @@
         <v>41</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="24">
-        <v>5</v>
-      </c>
-      <c r="D37" s="45"/>
-      <c r="E37" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="I37" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" s="28" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3538,18 +3505,18 @@
     <mergeCell ref="A3:A5"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="E6:J24">
+  <conditionalFormatting sqref="E6:J23">
     <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>$C6=E$3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E25:J37">
+  <conditionalFormatting sqref="E24:J36">
     <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$C26=E$3</formula>
+      <formula>$C25=E$3</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C37" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C36" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$E$3:$J$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -3562,7 +3529,7 @@
           <x14:formula1>
             <xm:f>'Team and Self Assessment'!$C$10:$C$17</xm:f>
           </x14:formula1>
-          <xm:sqref>B6:B37</xm:sqref>
+          <xm:sqref>B6:B36</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4751,23 +4718,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010097D51C9FBC39324EBAB59B01C4346E09" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7b26372eee874d7f4c5a56df6f7c7ecb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xmlns:ns4="fe0433fa-6222-408a-8cda-04e271f5cb7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5c97cb8d9fdd9979f1f4b37be720903" ns3:_="" ns4:_="">
     <xsd:import namespace="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
@@ -4956,25 +4906,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0018C3F5-B04E-47AD-B664-46B81F9081B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4991,4 +4940,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
+++ b/sem3_PI_2024-2025_TeamSelf-Assessment_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gonçalo\IdeaProjects\sem3-pi-2024_25_G145_v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ligui\OneDrive\Ambiente de Trabalho\sem3-pi-2024_25_G145_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F77DCC4-1F32-416E-B43A-84552096950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD0A17C2-2949-4896-8292-E3D1754F0629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1035" yWindow="3510" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team and Self Assessment" sheetId="2" r:id="rId1"/>
@@ -52,9 +52,9 @@
   <commentList>
     <comment ref="A5" authorId="0" shapeId="0" xr:uid="{6BAF2E2E-33D1-44DF-B745-43730409185A}">
       <text>
-        <t>[Comentário por tópicos]
-A sua versão do Excel permite-lhe ler este comentário por tópicos. No entanto, as edições feitas ao comentário serão removidas se o ficheiro for aberto numa versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Proposta: Documentation em vez de "Project Report &amp; Documentation"</t>
       </text>
     </comment>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="169">
   <si>
     <t>LAPR3 Project Team and Self-assessment v4.0</t>
   </si>
@@ -625,6 +625,12 @@
   </si>
   <si>
     <t>USAC10</t>
+  </si>
+  <si>
+    <t>USFA01</t>
+  </si>
+  <si>
+    <t>USFA02</t>
   </si>
 </sst>
 </file>
@@ -1397,9 +1403,29 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1646,7 +1672,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2472,7 +2498,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultColWidth="20.125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
@@ -3497,6 +3523,66 @@
         <v>43</v>
       </c>
     </row>
+    <row r="37" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="24">
+        <v>5</v>
+      </c>
+      <c r="D37" s="45"/>
+      <c r="E37" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="24">
+        <v>5</v>
+      </c>
+      <c r="D38" s="45"/>
+      <c r="E38" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="D3:D5"/>
@@ -3506,17 +3592,27 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="E6:J23">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="3" stopIfTrue="1">
       <formula>$C6=E$3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:J36">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="5" stopIfTrue="1">
       <formula>$C25=E$3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E37:J37">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+      <formula>$C38=E$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38:J38">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$C39=E$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C36" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C38" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>$E$3:$J$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -3529,7 +3625,7 @@
           <x14:formula1>
             <xm:f>'Team and Self Assessment'!$C$10:$C$17</xm:f>
           </x14:formula1>
-          <xm:sqref>B6:B36</xm:sqref>
+          <xm:sqref>B6:B38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4718,6 +4814,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010097D51C9FBC39324EBAB59B01C4346E09" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7b26372eee874d7f4c5a56df6f7c7ecb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xmlns:ns4="fe0433fa-6222-408a-8cda-04e271f5cb7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e5c97cb8d9fdd9979f1f4b37be720903" ns3:_="" ns4:_="">
     <xsd:import namespace="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
@@ -4906,24 +5019,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d1820d08-fbb8-4f42-a1d4-888ae23d26d1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0018C3F5-B04E-47AD-B664-46B81F9081B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4940,22 +5054,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D8D82CB-2E6F-4A14-B6B4-DFDD1BBD70FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d1820d08-fbb8-4f42-a1d4-888ae23d26d1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F61419B8-A98A-41CD-95EE-48A4F975B8D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>